--- a/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
+++ b/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
@@ -530,19 +530,25 @@
     <t>어드민 스토어 목록에 알리페이 노출 칼럼과 사유 칼럼을 추가한다. 상품 목록(BO-CH-02)과 같은 패턴이다.</t>
   </si>
   <si>
-    <t xml:space="preserve">■ 목록 칼럼
-- 위치 : 스토어명 바로 뒤
+    <t xml:space="preserve">■ 목록 구조 (실측)
+- 원본 탭 + 언어 탭 6개(중국어(간체) / 영어 / 중국어(번체) / 일본어 / 인도네시아어 / 몽골어)
+- 원본 탭 칼럼 : No. / 공개여부 / 등록일 / 스토어명 / [알리페이 노출] / [사유] / 카테고리 / 지원언어 / 노출수 / 클릭수 / 조회수 / 채팅수 / 상담수 / 버튼 클릭수 / 예약 설정 / 관리
+- 언어 탭 칼럼 : 스토어명 / 카테고리 / 언어 / [알리페이 노출] / [사유] / 노출 / 상품 수
+■ 목록 칼럼
+- 위치 : 스토어명 바로 뒤 (원본 탭), 언어 뒤 (언어 탭)
 - 알리페이 노출 : 노출 / 미노출
 - 사유 : 스토어에 나오는 값 = 미노출 설정 / 알리페이 버튼 미설정
+- 원본 탭과 중국어(간체)·영어·중국어(번체) 탭에만 둔다. 일본어·인도네시아어·몽골어 탭에는 없음
 ■ 필터
-- 알리페이 노출 셀렉트, 사유 셀렉트</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- 스토어는 언어와 무관한 한 건이라 언어에 따라 결과가 갈리지 않는다
+- 공개여부 선택 뒤에 알리페이 노출 셀렉트, 사유 셀렉트
+- 일본어·인도네시아어·몽골어 탭으로 바꾸면 두 필터는 전체로 돌아가 잠긴다(BO-CH-02와 같은 방식)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- 스토어의 알리페이 값은 언어와 무관한 한 건이라 어느 탭에서나 같다
 - 사유 미노출 설정인 스토어의 상품도, 사유 알리페이 버튼 미설정인 스토어의 상품도 전부 사유 "스토어 미노출"로 미노출</t>
   </si>
   <si>
-    <t>PRD v2.15 8장. 그림 4 패턴. 원본 화면 = 라이브 어드민 스토어 목록</t>
+    <t>PRD v2.15 8장. 그림 4 패턴. 원본 화면 = 라이브 어드민 스토어 목록 2026-09-18 실측(원본 탭 + 언어 탭)</t>
   </si>
   <si>
     <t>배너 관리</t>
@@ -3127,7 +3133,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="20" ht="85" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" ht="166" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>

--- a/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
+++ b/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
@@ -247,7 +247,7 @@
   </si>
   <si>
     <t xml:space="preserve">- 배너·기획전도 같다. 스토어는 언어 무관이라 해당 없음
-- 목록의 해당 언어 탭에서는 알리페이 노출·사유 칼럼에 "-"</t>
+- 목록에서 해당 언어를 고르면 알리페이 노출·사유 칼럼에 "-"</t>
   </si>
   <si>
     <t>PRD v2.15 1장·6장·10장</t>
@@ -336,7 +336,7 @@
 - 알리페이 노출 : 셀렉트 (전체 / 노출 / 미노출)
 - 사유 : 셀렉트 (전체 / 미노출 설정 / 스토어 미노출 / 알리페이 버튼 미설정)
 ■ 언어
-- 목록의 언어 탭 기준. 그 언어 건들의 결과가 보인다. 일본어·인도네시아어·몽골어 탭(원본 탭이 있으면 그것도)은 두 칼럼 "-" + 필터 비활성</t>
+- 언어 필터에서 고른 언어 건들의 결과가 보인다. 일본어·인도네시아어·몽골어를 고르면 두 칼럼 "-" + 두 필터 비활성</t>
   </si>
   <si>
     <t xml:space="preserve">- 미노출 설정은 사람이 다시 켜야 하고, 나머지는 조건이 풀리면 저절로 노출로 바뀐다
@@ -799,7 +799,7 @@
 ■ 필터
 - 알리페이 노출 셀렉트, 사유 셀렉트
 ■ 언어
-- 목록의 언어 탭 기준</t>
+- 목록의 언어 필터 기준</t>
   </si>
   <si>
     <t xml:space="preserve">- 알리페이 버튼 미설정은 랜딩페이지형 배너에만 나온다
@@ -1021,7 +1021,7 @@
 ■ 필터
 - 알리페이 노출 셀렉트, 사유 셀렉트
 ■ 언어
-- 목록의 언어 탭 기준</t>
+- 목록의 언어 필터 기준</t>
   </si>
   <si>
     <t>- 노출 대상 없음은 그 기획전이 담은 항목이 전부 알리페이에서 숨겨진 상태. 병원 유형은 스토어를, 나머지 유형은 상품을 센다</t>

--- a/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
+++ b/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
@@ -90,7 +90,7 @@
   ㄴ 상품에는 예약 행이 없다
   ㄴ 알리페이 열의 외부링크·메신저는 비활성 고정(OFF) + 안내 “알리페이 앱 미지원 항목입니다.”
   ㄴ 상담접수와 채팅은 서로 완전히 독립된 항목이다. 통합 표시도 독립된 값으로 상담접수·채팅 상태와 무관하게 언제나 켜고 끌 수 있다
-  ㄴ 항목마다 프런트 하단의 독립된 자리다. 상담접수, 채팅, 통합 표시가 켜져 있으면 각각 한 자리를 쓴다. 통합 표시는 기존 문의하기 버튼 그대로이며, 다른 항목의 값을 읽거나 대신 세어지지 않는다. 화면에서 어느 행도 잠그거나 배지를 붙이지 않는다
+  ㄴ 항목마다 프런트 하단의 독립된 자리다. 상담접수, 채팅, 통합 표시가 켜져 있으면 각각 한 자리를 쓴다. 통합 표시는 기존 문의하기 버튼 그대로이며, 다른 항목의 값을 읽거나 대신 세어지지 않는다. 상담접수·채팅·통합 표시 세 행은 서로 잠그거나 배지를 붙이지 않는다
   ㄴ 자리 수는 열마다 최대 둘. 켜져 있는 유효 항목 수가 곧 자리 수다. 셋째 자리를 만들려 하면 화면 위쪽 알림으로 막고 토글은 원위치. 예약을 다시 사용으로 바꿔 셋째가 되면 빨간 안내가 뜨고 저장이 막힌다
   ㄴ 상한·조건 ②·자리 수 표기는 저장값이 아니라 유효값 기준. 상담접수·채팅·통합 표시는 서로 독립된 값이라 저장값 자체에 강제로 맞춰야 하는 조합이 없다
 - 안내 박스 : 알리페이 열에 ON이 없으면 “알리페이 앱 버튼이 없어 알리페이에 노출되지 않습니다. 버튼 설정에서 1개 이상 켜면 노출됩니다.”
@@ -214,7 +214,7 @@
   </si>
   <si>
     <t xml:space="preserve">■ 초기값 규칙
-- 웹에서 켠 상담접수·문의하기 통합·채팅 → 알리페이 열도 ON
+- 웹에서 켠 상담접수·채팅·상담접수·채팅 통합 표시 → 알리페이 열도 ON
 - 웹에서 켠 외부링크·메신저 → 알리페이 열 OFF(비활성)
 - 메신저만 켠 상품이면 알리페이 열이 비어서 시작. 안내 박스(e3) 즉시 표시
 ■ 이후
@@ -374,7 +374,7 @@
   ㄴ 예약은 예약설정 탭에서 예약을 켠 뒤에만. 웹·알리페이 열 모두 같다
   ㄴ 항목마다 프런트 하단 독립된 자리. 서로 묶어 세는 항목 없음. 자리 수는 열마다 최대 둘
 - 메신저 채널·URL·QR : 기존 언어별 구조 그대로. 알리페이 열과 무관
-- 안내 박스 : 알리페이 열 ON 없음 시 "알리페이 앱 버튼이 없어 알리페이에 노출되지 않습니다.” 기본정보 탭에서는 “알리페이 앱 버튼이 없어 알리페이에 노출되지 않습니다. 버튼 및 메신저 설정에서 1개 이상 켜면 노출됩니다."
+- 안내 박스 : 알리페이 열 ON 없음 시 "알리페이 앱 버튼이 없어 알리페이에 노출되지 않습니다.” 기본정보 탭에서는 “알리페이 앱 버튼이 없어 이 스토어와 스토어 상품 N건이 알리페이에 노출되지 않습니다. 버튼 및 메신저 설정에서 1개 이상 켜면 노출됩니다."
 - 알리페이 노출이 노출인데 알리페이 열에 ON이 없는 상태로 저장하면 저장 시 확인 "알리페이 앱 버튼이 없습니다. 저장하면 스토어가 알리페이에 노출되지 않습니다. 저장할까요?" 어떤 행을 꺼서 비었든 같다. 행을 끄는 순간에는 확인을 띄우지 않는다
 ■ 기본정보 탭 · 미노출 선택 시
 - 라디오 아래 안내 박스 "미노출로 저장하면 이 스토어 상품 N건도 알리페이에 노출되지 않습니다." 고르는 순간에는 확인을 띄우지 않는다
@@ -419,7 +419,7 @@
   </si>
   <si>
     <t xml:space="preserve">■ 안내 박스
-- “알리페이 앱 버튼이 없어 알리페이에 노출되지 않습니다.” 기본정보 탭에서는 “알리페이 앱 버튼이 없어 알리페이에 노출되지 않습니다. 버튼 및 메신저 설정에서 1개 이상 켜면 노출됩니다.”</t>
+- “알리페이 앱 버튼이 없어 알리페이에 노출되지 않습니다.” 기본정보 탭에서는 “알리페이 앱 버튼이 없어 이 스토어와 스토어 상품 N건이 알리페이에 노출되지 않습니다. 버튼 및 메신저 설정에서 1개 이상 켜면 노출됩니다.”</t>
   </si>
   <si>
     <t>- 목록(BO-CH-04) 사유 = 알리페이 버튼 미설정</t>
@@ -917,7 +917,7 @@
 - 유형을 바꾸면 그 기획전이 붙는 유형 레코드도 같은 언어의 새 유형으로 옮겨진다. 같은 언어에 그 유형 레코드가 없으면 어느 유형에도 붙지 않는다
 - 담는 종류가 달라지는 유형으로 바꾸면 앞 유형에 담아 둔 항목은 비운다. 추천상품·특가·TOP10 사이의 전환은 담은 상품을 유지한다. 확인 문구 "유형을 변경하면 담은 상품 N건이 삭제되고 스토어만 담을 수 있습니다. 스토어를 1개 이상 담아야 저장할 수 있습니다. 변경할까요?" 병원에서 상품 유형으로 바꿀 때는 상품과 스토어를 바꿔 쓴다. 비운 상태로는 저장할 수 없어 그 자리에서 새 유형의 항목을 담아야 한다
 - 안의 항목이 다시 생기면 별도 조작 없이 노출
-- 담은 것이 있는데 전부 보이지 않는 경우는 차단하지 않는다. 원인이 그 상품·스토어 쪽 설정이라 이 화면에서 고칠 수 없고, 대상이 돌아오면 기획전도 자동 복구된다. 차단은 버튼 개수 상한 초과와 구성 항목 0건
+- 담은 것이 있는데 전부 보이지 않는 경우는 차단하지 않는다. 원인이 그 상품·스토어 쪽 설정이라 이 화면에서 고칠 수 없고, 대상이 돌아오면 기획전도 자동 복구된다. 이 화면의 차단은 구성 항목 0건
 - 저장 검사 순서 = ① 버튼 개수 상한 → ② 구성 항목 0건 → ③ 확인(기획전은 노출 가능 항목 0건). ①②에 걸리면 확인을 띄우지 않고 막는다
 - 대상 언어(중국어(간체)·중국어(번체)·영어)가 아닌 기획전은 알리페이 노출 라디오가 노출로 고정 잠김. 안내 문구는 두지 않는다
 - 구성 항목 표의 체크박스로 여러 건을 고를 수 있다. 하나도 고르지 않으면 선택 삭제 버튼은 비활성</t>
@@ -1057,7 +1057,7 @@
 - 상담접수 : 가능 (자체 기능). 채팅과 완전히 독립
 - 채팅 : 가능. 인앱 채팅, 웹 열에서도 켤 수 있다. 상담접수와 완전히 독립
 - 상담접수·채팅 통합 표시 : 가능. 기존 문의하기 버튼 그대로. 다른 항목과 같은 독립된 버튼이라 켜면 1자리. 다른 항목의 값을 읽지 않는다
-- 표에서 어느 행도 잠그거나 배지를 붙이지 않는다. 모든 항목이 항상 조작할 수 있는 평범한 라디오다
+- 상담접수·채팅·통합 표시 세 행은 서로 잠그거나 배지를 붙이지 않는다. 잠금은 외부링크·메신저의 알리페이 열, 예약 미사용, 기본 설정, 미노출 상태에만 있다
 - 통합 표시 행 오른쪽에는 상시 “기존 문의하기 버튼입니다. 다른 항목과 같이 독립된 버튼이라 켜면 1개로 셉니다.”
 - 외부링크 설정 : 비활성 고정 + 안내 “알리페이 앱 미지원 항목입니다.”
 - 메신저 설정 : 비활성 고정 + 같은 안내. 채널·URL·QR 입력은 기존 언어별 구조 그대로. 언어별 입력 영역 안내는 “메신저 설정을 켜면 언어별로 1개씩 등록할 수 있습니다.”
@@ -1099,7 +1099,7 @@
 - 잠금 문구(표 아래 한 줄, 하나만 노출. 위에서부터 먼저 걸리는 것) : 기본 설정 잠금 → 알리페이 노출 미노출 잠금
 - 상품이 속한 스토어 미노출은 알리페이 노출 라디오 아래 한 줄로 갈음하고 표 아래에 두지 않는다
 ■ 안내 박스
-- 알리페이 열 ON 없음(잠금 없음) : “알리페이 앱 버튼이 없어 알리페이에 노출되지 않습니다. 버튼 설정에서 1개 이상 켜면 노출됩니다.”</t>
+- 알리페이 열 ON 없음(잠금 없음) : “알리페이 앱 버튼이 없어 알리페이에 노출되지 않습니다. 버튼 설정에서 1개 이상 켜면 노출됩니다.” 스토어의 버튼 및 메신저 설정 섹션에서는 첫 문장만 쓴다</t>
   </si>
   <si>
     <t>- BO-CH-10 에서 뗀 절이다. 표 구조·항목 규칙·상한은 BO-CH-10 을 본다</t>
@@ -1206,7 +1206,7 @@
 - 칼럼 재배치, 필터 신설, 정렬 변경</t>
   </si>
   <si>
-    <t xml:space="preserve">- 표기 위치와 형태는 각 화면 실측 자료를 받아 확정한다. 2026-09-15 기준 미확정
+    <t xml:space="preserve">- 표기 위치와 형태는 각 화면 실측 자료를 받아 확정한다. 실측 자료 수령 전이라 미확정
 - 쿠폰과 통계는 이번 범위가 아니다. 집계는 두 집합을 합쳐 하나로 센다</t>
   </si>
   <si>
@@ -1844,7 +1844,7 @@
 - 여권 영문명. 알리페이가 주는 이름은 여권 표기가 보장되지 않는다. 직접 입력받는다
 ■ 그대로 두는 것
 - 휴대폰 번호 문자 인증. 현행 그대로 필수
-- 메신저 연락처 입력. 현행 그대로 필수. 앱 열기 버튼만 숨긴다(FO-CH-05-e1)
+- 메신저 연락처 입력. 현행 그대로 필수. 앱 열기 버튼만 숨긴다(FO-CH-05-e2)
 - 요청사항. 선택
 ■ 예약 요청 버튼
 - 이메일을 포함해 위 필수 항목이 모두 채워져야 활성화된다
@@ -1884,7 +1884,7 @@
 - 목록의 노출 결과와 사유가 다시 계산되는 경우는 PRD 9장 목록 7종
 - 최초 일괄 계산과 전체 재계산 순서 = 스토어 → 상품 → 기획전·인플루언서 기획전 → 배너. 순환 참조 없음
 ■ 버튼
-- 종류 : 상담접수 / 문의하기 통합 / 채팅(신설) / 외부링크 / 메신저 / 예약. 상품·스토어
+- 종류 : 상담접수 / 채팅(신설) / 상담접수·채팅 통합 표시 / 외부링크 / 메신저 / 예약. 상품·스토어
 - 채널 구분 : 상품·스토어는 버튼마다, 배너는 하단 버튼 하나에 웹 값과 알리페이 값을 각각 가진다
 - 배너 하단 버튼 링크 종류에 내부링크 추가 + 연결 대상(종류 · 이름)을 고른다. 종류는 직접입력·병원·기획전·인플루언서. 배너 링크종류 외부링크 판정은 지금 값을 그대로 읽는다
 - 상품의 스토어 설정 적용(개별 설정 / 기본 설정)은 지금 구조 그대로. 기본 설정이면 알리페이 값도 스토어 값을 따른다
@@ -1921,7 +1921,7 @@
 - 내부링크 대상(병원·기획전·인플루언서·패턴에 맞는 직접입력)이 알리페이 미노출인 배너 → 사유 노출 대상 없음. 패턴에 맞지 않는 직접입력만 판정하지 않음
 - 노출 가능 항목이 0건인 기획전(조건 ④) → 사유 노출 대상 없음
 ■ 사유 산출 (미노출 행)
-- 미노출 설정 / 스토어 미노출(상품이 속한 스토어의 노출 설정 미노출) / 외부 사이트 연결 / 알리페이 버튼 미설정 / 노출 대상 없음. 이 순서로 하나만 표시
+- 미노출 설정 / 스토어 미노출(상품이 속한 스토어의 판정이 미노출. 설정 미노출 또는 알리페이 버튼 미설정) / 외부 사이트 연결 / 알리페이 버튼 미설정 / 노출 대상 없음. 이 순서로 하나만 표시
 - 기본 설정 상품의 ② = 스토어 알리페이 열에서 예약을 뺀 값, 비면 채팅 자동 ON으로 통과
 - 판정 실패(대상 조회 오류) = 직전 판정값 유지. 나중에 다시 계산. 사유를 만들지 않는다
 ■ 설정값 보존
@@ -1952,15 +1952,15 @@
   <si>
     <t xml:space="preserve">■ 선행 산출물 (배치 전)
 - (a) 해당 없음. 상담접수·채팅·통합 표시가 서로 독립된 값이라 “상담접수 OFF + 통합 표시 ON” 조합도 유효한 상태다. 정리 대상이 아니다
-- (b) 웹 버튼 자리 3개 이상 건 집계 → 켜 둔 항목 수가 곧 자리 수. 지금 웹은 상담접수와 문의하기를 1개로 세지만 새 규칙은 2개라, 이 둘에 예약·메신저가 더 켜진 건이 걸린다. 배포 전 개발이 건수를 먼저 뽑아 공유한다. 값 유지, 목록으로 넘겨 사장님이 배포 전에 2개로 정리를 마친다
+- (b) 웹 버튼 자리 3개 이상 건 집계 → 켜 둔 항목 수가 곧 자리 수. 지금 웹은 상담접수와 문의하기를 1개로 세지만 새 규칙은 2개라, 이 둘에 예약·메신저·외부링크가 더 켜진 건이 걸린다. 배포 전 개발이 건수를 먼저 뽑아 공유한다. 값 유지, 목록으로 넘겨 사장님이 배포 전에 2개로 정리를 마친다
 - (c) 구성 항목 0건 기획전 집계 → 값 유지, 목록으로 넘겨 사장님이 배포 전에 항목을 담거나 비활성으로 정리를 마친다
 - (d) 연결 대상이 비활성·기간 종료·언어 불일치인 배너 집계 → 배포와 동시에 알리페이 미노출로 바뀜. 배너 자체가 기간 종료면 제외. 이미 웹에서도 안 보이는 대상이라 정리를 기다리지 않고 배포한다
 - (e) 같은 유형 값·언어로 둘 이상인 기획전 유형 레코드 집계 → 사장님이 배포 전에 하나로 합치고 붙은 기획전·가리키는 배너를 남는 레코드로 이동해 정리를 마친다. 값 유지
 ■ 알리페이 열 채우기 규칙
-- 웹 ON인 상담접수·문의하기 통합·예약 → 알리페이 ON
+- 웹 ON인 상담접수·상담접수·채팅 통합 표시·예약 → 알리페이 ON
 - 웹 메신저 ON → 알리페이 채팅 ON
 - 외부링크 → 알리페이 OFF
-- 배너 하단 버튼 : 버튼 링크 종류 외부링크 → 알리페이 비활성화, 링크없음 → 웹 값 그대로
+- 배너 하단 버튼 : 버튼 링크 종류 외부링크 → 알리페이 비활성화, 내부링크·링크없음 → 웹 값 그대로
 - 기본 설정 상품 → 알리페이 열 따로 만들지 않음. 스토어 값에서 예약을 뺀 것, 비면 채팅 자동 ON
 - 채팅은 기존 값이 없어 위 규칙으로만 채워짐
 ■ 결과·일괄 처리·배포 순서·롤백

--- a/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
+++ b/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="468">
   <si>
     <t>K-Beauty Station 알리페이 채널 분기 기능정의서 v2.16 (PRD v2.15 기준, 2026-09-18)</t>
   </si>
@@ -214,7 +214,7 @@
   </si>
   <si>
     <t xml:space="preserve">■ 초기값 규칙
-- 웹에서 켠 상담접수·채팅·상담접수·채팅 통합 표시 → 알리페이 열도 ON
+- 웹에서 켠 상담접수, 채팅, 상담접수·채팅 통합 표시 → 알리페이 열도 ON
 - 웹에서 켠 외부링크·메신저 → 알리페이 열 OFF(비활성)
 - 메신저만 켠 상품이면 알리페이 열이 비어서 시작. 안내 박스(e3) 즉시 표시
 ■ 이후
@@ -341,7 +341,7 @@
   <si>
     <t xml:space="preserve">- 미노출 설정은 사람이 다시 켜야 하고, 나머지는 조건이 풀리면 저절로 노출로 바뀐다
 - 사유는 지금 보고 있는 언어 기준. 다른 언어 건은 노출 중일 수 있다
-- 두 칼럼은 판정 결과(SYS-CH-01)를 보여준다. 값을 산출하는 판정 조건은 SYS-CH-02
+- 두 칼럼은 판정 결과(SYS-CH-02)를 보여준다. 값을 산출하는 판정 조건은 SYS-CH-02
 - 저장하면 목록과 고객 화면에 즉시 반영된다. 참조 대상이 바뀌어 결과가 달라지는 경우도 같다</t>
   </si>
   <si>
@@ -386,7 +386,7 @@
   <si>
     <t xml:space="preserve">- 스토어의 알리페이 노출 설정이 미노출이면 그 스토어의 상품이 모든 언어에서 함께 숨겨진다(조건 ③). 스토어를 되돌리면 그 스토어의 상품은 원래 값대로 돌아온다
 - 스토어의 알리페이 열이 비면 스토어와 그 스토어의 상품이 모두 숨겨진다(조건 ③). 이때 기본정보 탭 알리페이 노출 라디오 아래에 “알리페이 앱 버튼이 없어 이 스토어와 스토어 상품 N건이 알리페이에 노출되지 않습니다. 버튼 및 메신저 설정에서 1개 이상 켜면 노출됩니다.” 안내를 둔다
-- 스토어가 노출이고 알리페이 열에 예약만 켜져 있으면 기본 설정 상품은 채팅 자동 ON으로 노출. 이때 라디오 아래에 “기본 설정을 쓰는 상품 N건은 알리페이 앱에서 채팅이 자동으로 켜져 노출됩니다. 예약을 뺀 알리페이 앱 버튼이 없어서입니다.” 안내를 둔다
+- 스토어가 노출이고 알리페이 열에 예약만 켜져 있으면 기본 설정 상품은 채팅 자동 ON으로 노출. 이때 라디오 아래에 “기본 설정을 쓰는 상품 N건은 알리페이 앱에서 채팅이 자동으로 켜져 노출됩니다. 예약을 뺀 알리페이 앱 버튼이 없어서입니다.” 안내를 둔다. N은 알리페이 대상 언어 상품만 센다
 - 스토어의 알리페이 버튼 설정 변경은 기본 설정인 상품 전부에 즉시 적용
 - 공개 여부가 비공개여도 알리페이 노출 라디오를 잠그지 않는다. 신규 스토어가 비공개로 시작하므로 공개 전에 미리 정해 둘 수 있어야 한다. 안내 문구도 없음</t>
   </si>
@@ -894,7 +894,7 @@
 - 상품 표 : 체크박스·No.·상품명·언어·스토어명(언어)·가격·노출수·클릭수·조회수·스토어 활성화·상품 활성화·히든·action
 - 스토어 표 : 체크박스·스토어명·조회수·클릭수·action
 - 빈 상태 : "선택된 상품 정보가 없습니다" / "선택된 스토어 정보가 없습니다"
-- 추가 : 두 표 모두에 알리페이 노출 칼럼. 상품 표는 스토어명(언어) 바로 뒤, 스토어 표는 클릭수 바로 뒤. 값은 각 항목의 저장된 판정 결과(SYS-CH-01)를 읽어 보여주며 이 모달에서 편집하지 않는다
+- 추가 : 두 표 모두에 알리페이 노출 칼럼. 상품 표는 스토어명(언어) 바로 뒤, 스토어 표는 클릭수 바로 뒤. 값은 각 항목의 저장된 판정 결과(SYS-CH-02)를 읽어 보여주며 이 모달에서 편집하지 않는다
 - 조건 ④는 그 기획전이 담는 종류만 센다. 병원은 스토어, 나머지 유형은 상품
 - 기획전에는 본문 에디터가 없어 링크 차단 대상이 아니다
 ■ 안내 박스 (해당 시)
@@ -973,6 +973,9 @@
   </si>
   <si>
     <t>- 유형 관리 화면의 다른 항목은 손대지 않는다</t>
+  </si>
+  <si>
+    <t>PRD v2.15 7장 배너 절. 동작 시안 없음(유형 관리는 기존 화면에 검증 하나만 추가). STG에서 확인</t>
   </si>
   <si>
     <t>노출 가능 항목 0건 저장 확인 모달</t>
@@ -1079,7 +1082,7 @@
 - 채팅 버튼 라벨은 기존 인앱 채팅 진입 문구를 언어별로 그대로 사용, 채팅방은 상품이 속한 스토어 기준</t>
   </si>
   <si>
-    <t>PRD v2.15 7장. 그림 2·3. 원본 화면 = 라이브 어드민 스토어 버튼 및 메신저 설정(ON/OFF 라디오 항목형, 실측 2026-09-03)</t>
+    <t>PRD v2.15 7장. 그림 2·3. 원본 화면 = 라이브 어드민 스토어 버튼 및 메신저 설정(ON/OFF 라디오 항목형, 실측 2026-09-03). 셋째 버튼 토스트 Figma St_bo03_e5, 상한 초과 저장 차단 Figma mdl_bo10_alert</t>
   </si>
   <si>
     <t>버튼 설정 영역의 안내 문구 규칙</t>
@@ -1200,7 +1203,7 @@
 - 리뷰 관리 (목록)
 ■ 표기
 - 회원을 가리키는 자리에 알리페이 회원임을 알 수 있는 표시를 함께 둔다
-- 알리페이 회원은 이름이 없을 수 있다. 그때는 알리페이 식별자를 표시한다
+- 알리페이 회원은 이름이 없을 수 있다. 그때는 알리페이 식별자를 표시한다(어드민 화면만. 고객 화면은 "알리페이 회원", FO-CH-04)
 - 기존 회원은 지금 그대로 둔다. 표시를 더하지 않는다
 ■ 하지 않는 것
 - 칼럼 재배치, 필터 신설, 정렬 변경</t>
@@ -1475,7 +1478,7 @@
     <t xml:space="preserve">■ 대상 채널
 - 왓츠앱, 라인, 위챗, 카카오 네 채널 모두 동일
 ■ 유지
-- 아이디 입력 필드</t>
+- 아이디 입력 필드. placeholder "메신저 아이디를 직접 입력해 주세요"</t>
   </si>
   <si>
     <t>- 메신저 도메인은 알리페이 화이트리스트에 신청하지 않는다</t>
@@ -1520,7 +1523,7 @@
     <t>FO-CH-05-e4</t>
   </si>
   <si>
-    <t>상품이 속한 스토어의 판정(SYS-CH-02)이 미노출이면 그 상품은 자기 설정·버튼과 무관하게 알리페이에 노출되지 않는다(SYS-CH-01 조건 ③). 상품 상세는 FO-CH-03과 같이 404로 처리한다.</t>
+    <t>상품이 속한 스토어의 판정(SYS-CH-02)이 미노출이면 그 상품은 자기 설정·버튼과 무관하게 알리페이에 노출되지 않는다(조건 ③, FO-CH-02). 상품 상세는 FO-CH-03과 같이 404로 처리한다.</t>
   </si>
   <si>
     <t xml:space="preserve">■ 판정
@@ -1586,6 +1589,7 @@
 - 알리페이 중국 : alipay-app.kbstations.com/zh (간체)
 - 알리페이 홍콩 : alipay-app.kbstations.com/zh-TW (번체)
 ■ 언어 선택 목록
+- 제목 아래 안내 "보고 싶은 언어를 선택해 주세요."
 - 남김 : 중국어 간체 / 영어 / 중국어 번체. 이 순서(진입 언어 둘 사이에 영어)
 - 제외 : 일본어 / 몽골어 / 인도네시아어
 ■ 대상 외 언어 경로
@@ -1618,7 +1622,7 @@
   </si>
   <si>
     <t xml:space="preserve">■ 프로필 영역 (알리페이 채널, 프로필 제공을 거부한 회원만)
-- 불러오기 버튼 1개 + 짧은 설명 (알리페이 계정의 이름·성별·생년월일·국적을 가져온다는 안내)
+- 보조문 "이름, 성별, 생년월일, 국적이 아직 없습니다." + 보조 버튼 "알리페이 계정에서 불러오기" + 회색 안내 "알리페이 계정의 이름, 성별, 생년월일, 국적을 가져옵니다. 이메일과 전화번호는 가져오지 않습니다."
 - 누르면 프로필 제공 항목만 담은 동의 창(FO-CH-08-mdl)을 한 번 더 띄운다
   ㄴ 동의 : 프로필 채움, 동의 여부 갱신, 버튼 사라짐
   ㄴ 거부 : 그대로 유지
@@ -1673,7 +1677,7 @@
     <t xml:space="preserve">■ 모달
 - 제목 "알리페이 프로필 제공"
 - 본문 : 가져오는 항목(이름·성별·생년월일·국적) 안내 + 이메일·전화번호는 가져오지 않는다는 한 줄
-- 버튼 : 거부 / 동의(주)
+- 버튼 : 동의(주) / 거부. 세로 배치, 주 버튼 위
 ■ 결과
 - 동의 : 프로필 채움, 프로필 동의 여부를 동의로 갱신, 불러오기 버튼 사라짐
 - 거부 : 변화 없음. 마이페이지 그대로
@@ -1681,6 +1685,9 @@
   </si>
   <si>
     <t>- 필수 약관 항목은 다시 받지 않는다. 이미 회원이다</t>
+  </si>
+  <si>
+    <t>PRD v2.15 11장 프로필 처리. Figma fo08_mdl</t>
   </si>
   <si>
     <t>진입 동의 창 (약관 필수, 프로필·마케팅 선택)</t>
@@ -1702,8 +1709,8 @@
 ■ 항목 (넷)
 - 이용 약관 (필수)
 - 개인정보 처리방침 (필수)
-- 알리페이 프로필 제공 (선택). 이름·성별·생년월일·국적
-- 마케팅 정보 수신 (선택). 기존 회원과 같은 마케팅 수신동의 정책. 통로는 예약 시 입력한 이메일과 휴대폰 번호이며 메신저 연락처는 쓰지 않는다. 값이 비어 있는 동안은 동의만 받아 두고 발송 대상이 아니다
+- 알리페이 프로필 제공 (선택). 설명 "이름, 성별, 생년월일, 국적을 가져옵니다."
+- 마케팅 정보 수신 (선택). 설명 "K-Beauty Station의 혜택·이벤트 정보를 이메일, 휴대폰 번호로 받습니다." 기존 회원과 같은 마케팅 수신동의 정책. 통로는 예약 시 입력한 이메일과 휴대폰 번호이며 메신저 연락처는 쓰지 않는다. 값이 비어 있는 동안은 동의만 받아 두고 발송 대상이 아니다
 ■ 전문 보기
 - 항목 오른쪽 보기를 누르면 같은 모달 안에서 전문이 펼쳐지고 버튼이 접기로 바뀐다
 - 별도 페이지로 보내지 않는다. 펼쳐도 체크한 것은 풀리지 않는다
@@ -1754,6 +1761,8 @@
 - 그 밖에 로그인 화면으로 보내는 모든 자리
 ■ 직접 진입
 - 숨김이지 차단이 아니다. 로그인·회원가입 주소로 직접 들어오면 마이페이지로 보낸다
+■ 마이페이지 상단
+- 로그인 영역 자리에 이름(없으면 호칭 없음)과 "알리페이 계정으로 이용 중입니다."
 ■ 웹 채널
 - 그대로 둔다</t>
   </si>
@@ -1812,7 +1821,11 @@
 ■ 처리
 - 탈퇴하면 알리페이 식별자와의 연결을 끊는다
 - 다시 들어오면 같은 알리페이 계정이라도 새 회원으로 만든다. 진입 동의 창(FO-CH-09)을 다시 거친다
-- 보관과 파기는 기존 정책과 같다</t>
+- 보관과 파기는 기존 정책과 같다
+■ 화면 문구
+- 제목 "탈퇴하면 이렇게 됩니다" 아래 네 줄 : "알리페이 계정과의 연결이 끊깁니다." / "예약 내역과 채팅 기록을 볼 수 없습니다." / "다시 들어오면 같은 알리페이 계정이라도 새 회원으로 시작합니다." / "알리페이 앱 쪽 계정에는 아무 영향이 없습니다."
+- 안내 "보관과 파기는 개인정보처리방침을 따릅니다."
+- 버튼 "탈퇴하기". 확인 체크박스 없음</t>
   </si>
   <si>
     <t xml:space="preserve">- 탈퇴 직후 재진입하면 새 회원이 된다. 이전 예약 내역은 보이지 않는다. 탈퇴 확인 화면에 이 사실을 한 줄로 알린다
@@ -1957,7 +1970,7 @@
 - (d) 연결 대상이 비활성·기간 종료·언어 불일치인 배너 집계 → 배포와 동시에 알리페이 미노출로 바뀜. 배너 자체가 기간 종료면 제외. 이미 웹에서도 안 보이는 대상이라 정리를 기다리지 않고 배포한다
 - (e) 같은 유형 값·언어로 둘 이상인 기획전 유형 레코드 집계 → 사장님이 배포 전에 하나로 합치고 붙은 기획전·가리키는 배너를 남는 레코드로 이동해 정리를 마친다. 값 유지
 ■ 알리페이 열 채우기 규칙
-- 웹 ON인 상담접수·상담접수·채팅 통합 표시·예약 → 알리페이 ON
+- 웹 ON인 상담접수, 상담접수·채팅 통합 표시, 예약 → 알리페이 ON
 - 웹 메신저 ON → 알리페이 채팅 ON
 - 외부링크 → 알리페이 OFF
 - 배너 하단 버튼 : 버튼 링크 종류 외부링크 → 알리페이 비활성화, 내부링크·링크없음 → 웹 값 그대로
@@ -3655,7 +3668,7 @@
         <v>226</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>145</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" ht="85" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3669,28 +3682,28 @@
         <v>16</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>68</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36" ht="112" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3701,7 +3714,7 @@
         <v>206</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>16</v>
@@ -3710,22 +3723,22 @@
         <v>17</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="37" ht="368.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3733,10 +3746,10 @@
         <v>13</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>16</v>
@@ -3745,22 +3758,22 @@
         <v>17</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="38" ht="85" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3774,28 +3787,28 @@
         <v>16</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3809,28 +3822,28 @@
         <v>16</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>68</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="40" ht="260.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3838,34 +3851,34 @@
         <v>13</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" ht="139" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3873,10 +3886,10 @@
         <v>13</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>16</v>
@@ -3885,33 +3898,33 @@
         <v>17</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" ht="125.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>16</v>
@@ -3920,33 +3933,33 @@
         <v>17</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="43" ht="71.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>16</v>
@@ -3955,19 +3968,19 @@
         <v>17</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>198</v>
@@ -3975,153 +3988,153 @@
     </row>
     <row r="44" ht="85" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" ht="179.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" ht="44.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="47" ht="220" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C47" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="K47" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="48" ht="112" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>16</v>
@@ -4130,27 +4143,27 @@
         <v>17</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="49" ht="98.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>16</v>
@@ -4159,33 +4172,33 @@
         <v>16</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50" ht="58" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>16</v>
@@ -4194,33 +4207,33 @@
         <v>16</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="51" ht="85" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>16</v>
@@ -4229,33 +4242,33 @@
         <v>16</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="52" ht="85" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>16</v>
@@ -4264,74 +4277,74 @@
         <v>16</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="53" ht="152.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="54" ht="152.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="I53" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="K53" s="4" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="54" ht="139" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>293</v>
-      </c>
       <c r="B54" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>16</v>
@@ -4340,33 +4353,33 @@
         <v>17</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="55" ht="112" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>16</v>
@@ -4375,27 +4388,27 @@
         <v>17</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="56" ht="71.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>16</v>
@@ -4404,33 +4417,33 @@
         <v>16</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="57" ht="112" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>16</v>
@@ -4439,74 +4452,74 @@
         <v>16</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>68</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="58" ht="382" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="58" ht="395.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="59" ht="166" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="59" ht="193" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>16</v>
@@ -4515,33 +4528,33 @@
         <v>17</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="60" ht="166" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>16</v>
@@ -4550,33 +4563,33 @@
         <v>17</v>
       </c>
       <c r="F60" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="K60" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="G60" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="I60" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="J60" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="61" ht="85" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" ht="152.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>16</v>
@@ -4585,33 +4598,33 @@
         <v>17</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="62" ht="247" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>16</v>
@@ -4620,132 +4633,132 @@
         <v>17</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="63" ht="206.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="64" ht="166" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="65" ht="220" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="66" ht="274" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>16</v>
@@ -4754,63 +4767,63 @@
         <v>16</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F66" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="K66" s="6" t="s">
         <v>454</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>456</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="J66" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="K66" s="6" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="67" ht="314.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>

--- a/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
+++ b/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
@@ -83,7 +83,7 @@
 - 알리페이 노출 : 라디오 (노출 / 미노출), 디폴트 노출
   ㄴ 노출 = 웹과 알리페이 모두 노출
   ㄴ 미노출 = 웹에만 노출
-  ㄴ 스토어가 버튼 미설정으로 미노출이면 라디오 아래 안내 "스토어에 알리페이 앱 버튼이 없어 이 상품도 알리페이에 노출되지 않습니다. 스토어 정보 관리 &gt; 버튼 및 메신저 설정에서 1개 이상 켜면 노출됩니다." 라디오는 잠그지 않음
+  ㄴ 스토어가 버튼 미설정으로 미노출이면 라디오 아래 안내 "스토어에 알리페이 앱 버튼이 없어 이 상품도 알리페이에 노출되지 않습니다. 스토어 정보 관리 &gt; 버튼 및 메신저 설정에서 1개 이상 켜면 노출됩니다." 라디오와 알리페이 열 잠금(스토어 설정 미노출과 같음)
 ■ 버튼 설정 블록 (BO-CH-10 공통 구조)
 - 스토어 설정 적용 : 라디오 (개별 설정 / 기본 설정), 기존 그대로
 - 항목 표 : 행 = 상담접수 / 채팅(신설) / 상담접수·채팅 통합 표시 / 외부링크 설정 / 메신저 설정. 열 = 웹 ON·OFF 라디오, 알리페이 ON·OFF 라디오
@@ -262,7 +262,7 @@
     <t>BO-CH-01-e6</t>
   </si>
   <si>
-    <t>상품이 속한 스토어가 알리페이 미노출이면 이 상품의 알리페이 노출 값과 무관하게 상품은 알리페이에 노출되지 않는다(조건 ③). 알리페이 노출 라디오도 함께 잠근다. 버튼 설정의 알리페이 열은 잠긴 채 값을 보여준다. 스토어가 알리페이 버튼 미설정으로 미노출인 경우도 상품은 미노출(사유 스토어 미노출)이지만 라디오와 알리페이 열은 잠그지 않고 안내만 둔다.</t>
+    <t>상품이 속한 스토어가 알리페이 미노출이면 이 상품의 알리페이 노출 값과 무관하게 상품은 알리페이에 노출되지 않는다(조건 ③). 알리페이 노출 라디오도 함께 잠근다. 버튼 설정의 알리페이 열은 잠긴 채 값을 보여준다. 스토어가 알리페이 버튼 미설정으로 미노출인 경우도 같다. 상품은 미노출(사유 스토어 미노출), 라디오와 알리페이 열 잠금. 안내 문구만 다르다(BO-CH-01).</t>
   </si>
   <si>
     <t xml:space="preserve">■ 노출 설정 블록
@@ -386,7 +386,7 @@
   <si>
     <t xml:space="preserve">- 스토어의 알리페이 노출 설정이 미노출이면 그 스토어의 상품이 모든 언어에서 함께 숨겨진다(조건 ③). 스토어를 되돌리면 그 스토어의 상품은 원래 값대로 돌아온다
 - 스토어의 알리페이 열이 비면 스토어와 그 스토어의 상품이 모두 숨겨진다(조건 ③). 이때 기본정보 탭 알리페이 노출 라디오 아래에 “알리페이 앱 버튼이 없어 이 스토어와 스토어 상품 N건이 알리페이에 노출되지 않습니다. 버튼 및 메신저 설정에서 1개 이상 켜면 노출됩니다.” 안내를 둔다
-- 스토어가 노출이고 알리페이 열에 예약만 켜져 있으면 기본 설정 상품은 채팅 자동 ON으로 노출. 이때 라디오 아래에 “기본 설정을 쓰는 상품 N건은 알리페이 앱에서 채팅이 자동으로 켜져 노출됩니다. 예약을 뺀 알리페이 앱 버튼이 없어서입니다.” 안내를 둔다. N은 알리페이 대상 언어 상품만 센다
+- 스토어가 노출이고 알리페이 열에 예약만 켜져 있으면 기본 설정 상품은 채팅 자동 ON으로 노출. 스토어 화면에는 안내를 두지 않는다(상품 수정 화면의 채팅 행에만 안내)
 - 스토어의 알리페이 버튼 설정 변경은 기본 설정인 상품 전부에 즉시 적용
 - 공개 여부가 비공개여도 알리페이 노출 라디오를 잠그지 않는다. 신규 스토어가 비공개로 시작하므로 공개 전에 미리 정해 둘 수 있어야 한다. 안내 문구도 없음</t>
   </si>

--- a/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
+++ b/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
@@ -154,7 +154,7 @@
     <t>BO-CH-01-e2</t>
   </si>
   <si>
-    <t>기본 설정이면 웹 열과 알리페이 열 모두 스토어 값을 그대로 따른다. 두 열을 스토어 값으로 보여주고 편집을 잠근다. 상품에 없는 예약 행은 무시하고, 그렇게 읽은 알리페이 열이 비면 채팅을 자동 ON으로 본다.</t>
+    <t>기본 설정이면 웹 열과 알리페이 열 모두 스토어 값을 그대로 따른다. 두 열을 스토어 값으로 보여주고 편집을 잠근다. 상품에 없는 예약 행은 무시한다. 그렇게 읽은 알리페이 열이 비면 알리페이 버튼 미설정으로 미노출이다.</t>
   </si>
   <si>
     <t xml:space="preserve">■ 표시
@@ -165,7 +165,7 @@
 ■ 스토어 값 변경 시
 - 스토어의 알리페이 버튼 설정을 바꾸면 기본 설정인 상품 전부에 바로 적용된다
 ■ 예약만 켠 스토어
-- 알리페이 열에 채팅 ON(비활성)으로 표시. 채팅 행 오른쪽 "알리페이 앱 버튼이 없어 채팅이 자동 적용됩니다." 상품은 알리페이에 노출된다
+- 알리페이 열 전부 OFF(잠금). 표 아래 안내 “알리페이 앱 버튼이 없어 알리페이에 노출되지 않습니다. 개별 설정으로 바꾸거나 스토어의 버튼 및 메신저 설정에서 1개 이상 켜면 노출됩니다.” 상품은 알리페이 버튼 미설정으로 미노출
 ■ 개별 설정으로 전환
 - 웹 열은 스토어 현재 값을 그대로 이어받고, 알리페이 열만 비운 채 시작한다(웹 버튼 소실 방지). 알리페이 열이 비어 안내 박스가 바로 보인다</t>
   </si>
@@ -386,7 +386,7 @@
   <si>
     <t xml:space="preserve">- 스토어의 알리페이 노출 설정이 미노출이면 그 스토어의 상품이 모든 언어에서 함께 숨겨진다(조건 ③). 스토어를 되돌리면 그 스토어의 상품은 원래 값대로 돌아온다
 - 스토어의 알리페이 열이 비면 스토어와 그 스토어의 상품이 모두 숨겨진다(조건 ③). 이때 기본정보 탭 알리페이 노출 라디오 아래에 “알리페이 앱 버튼이 없어 이 스토어와 스토어 상품 N건이 알리페이에 노출되지 않습니다. 버튼 및 메신저 설정에서 1개 이상 켜면 노출됩니다.” 안내를 둔다
-- 스토어가 노출이고 알리페이 열에 예약만 켜져 있으면 기본 설정 상품은 채팅 자동 ON으로 노출. 스토어 화면에는 안내를 두지 않는다(상품 수정 화면의 채팅 행에만 안내)
+- 스토어가 노출이고 알리페이 열에 예약만 켜져 있으면 기본 설정 상품은 알리페이 열이 비어 미노출(사유 알리페이 버튼 미설정)
 - 스토어의 알리페이 버튼 설정 변경은 기본 설정인 상품 전부에 즉시 적용
 - 공개 여부가 비공개여도 알리페이 노출 라디오를 잠그지 않는다. 신규 스토어가 비공개로 시작하므로 공개 전에 미리 정해 둘 수 있어야 한다. 안내 문구도 없음</t>
   </si>
@@ -1240,7 +1240,7 @@
   </si>
   <si>
     <t xml:space="preserve">- 호스트 화면은 일반 유저 대상이라 어드민 용어(열, 구성, 조건 번호)를 쓰지 않는다
-- 호스트 등록 상품은 스토어 설정 적용 = 기본 설정으로 시작. 스토어 값(예약 제외, 비면 채팅 자동 ON)을 따르므로 안내가 뜨는 경우는 드물다
+- 호스트 등록 상품은 스토어 설정 적용 = 기본 설정으로 시작. 스토어 값(예약 제외)을 따른다. 스토어가 예약만 켰으면 알리페이 열이 비어 안내가 뜬다
 - 안내는 이 상품이 알리페이에 노출되지 않는 모든 경우에 뜬다(미노출 설정·스토어 미노출·알리페이 버튼 미설정). 대상 외 언어 건에는 없음
 - 미노출로 조정할 상품은 어드민이 BO-CH-01에서 바꾼다</t>
   </si>
@@ -1324,7 +1324,7 @@
   <si>
     <t xml:space="preserve">■ 판정 조건 (모두 만족해야 노출)
 - ① 그 건의 알리페이 노출 설정 = 노출
-- ② 알리페이 연결 : 상품·스토어는 알리페이 버튼 구성이 비어 있지 않음(기본 설정 상품은 스토어 값에서 예약을 뺀 것, 비면 채팅 자동 ON). 배너는 링크종류가 외부링크가 아니고, 랜딩페이지형이면 하단 버튼 알리페이 열 활성화, 내부링크 대상이 알리페이에 노출
+- ② 알리페이 연결 : 상품·스토어는 알리페이 버튼 구성이 비어 있지 않음(기본 설정 상품은 스토어 값에서 예약을 뺀 것). 배너는 링크종류가 외부링크가 아니고, 랜딩페이지형이면 하단 버튼 알리페이 열 활성화, 내부링크 대상이 알리페이에 노출
 - ③ 상품이 속한 스토어의 판정(SYS-CH-02)이 노출 (상품만). 스토어가 설정 미노출이든 버튼 미설정이든 미노출이면 상품도 미노출, 사유 스토어 미노출
 - ④ 노출 가능 항목 1건 이상 (기획전만). 병원 유형은 스토어를, 나머지 유형은 상품을 센다
 ■ 적용 노출면
@@ -1935,7 +1935,7 @@
 - 노출 가능 항목이 0건인 기획전(조건 ④) → 사유 노출 대상 없음
 ■ 사유 산출 (미노출 행)
 - 미노출 설정 / 스토어 미노출(상품이 속한 스토어의 판정이 미노출. 설정 미노출 또는 알리페이 버튼 미설정) / 외부 사이트 연결 / 알리페이 버튼 미설정 / 노출 대상 없음. 이 순서로 하나만 표시
-- 기본 설정 상품의 ② = 스토어 알리페이 열에서 예약을 뺀 값, 비면 채팅 자동 ON으로 통과
+- 기본 설정 상품의 ② = 스토어 알리페이 열에서 예약을 뺀 값. 비면 ② 불통
 - 판정 실패(대상 조회 오류) = 직전 판정값 유지. 나중에 다시 계산. 사유를 만들지 않는다
 ■ 설정값 보존
 - 판정으로 숨겨도 설정값은 건드리지 않는다</t>
@@ -1974,7 +1974,7 @@
 - 웹 메신저 ON → 알리페이 채팅 ON
 - 외부링크 → 알리페이 OFF
 - 배너 하단 버튼 : 버튼 링크 종류 외부링크 → 알리페이 비활성화, 내부링크·링크없음 → 웹 값 그대로
-- 기본 설정 상품 → 알리페이 열 따로 만들지 않음. 스토어 값에서 예약을 뺀 것, 비면 채팅 자동 ON
+- 기본 설정 상품 → 알리페이 열 따로 만들지 않음. 스토어 값에서 예약을 뺀 것. 비면 알리페이 버튼 미설정으로 미노출
 - 채팅은 기존 값이 없어 위 규칙으로만 채워짐
 ■ 결과·일괄 처리·배포 순서·롤백
 - 하위 행 SYS-CH-03-e1</t>
@@ -2005,7 +2005,7 @@
 - 외부링크만 켜진 상품 → 알리페이 열 비어 미노출 (현재 해당 상품 없음)
 - 외부링크 버튼 랜딩페이지 배너 → 미노출. 운영자가 내부링크로 바꾸고 알리페이 열 켜야 노출. 대상 목록은 검수 단계에서
 - 예약·메신저 켜진 스토어 → 노출
-- 예약만 켜진 스토어의 기본 설정 상품 → 채팅 자동 ON으로 노출
+- 예약만 켜진 스토어의 기본 설정 상품 → 알리페이 열이 비어 미노출. 스토어에서 상담접수나 채팅을 켜면 노출
 - 외부링크만 켜진 스토어 → 스토어와 그 스토어의 상품 전부 미노출(기본 설정 상품 포함)
 - 위반 건 처리 뒤 두 자리 상한 걸릴 일 없음 (메신저 → 채팅 1:1)
 ■ 일괄 처리
@@ -2656,7 +2656,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" ht="152.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" ht="166" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>13</v>
       </c>

--- a/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
+++ b/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
@@ -354,29 +354,29 @@
     <t>스토어 정보 수정 (알리페이 노출 설정, 채널별 버튼 구성)</t>
   </si>
   <si>
-    <t>BO 스토어 정보 수정 &gt; 기본정보 탭 / 버튼 및 메신저 설정 탭</t>
+    <t>BO 스토어 정보 수정 &gt; 기본정보 섹션 / 버튼 및 메신저 설정 섹션</t>
   </si>
   <si>
     <t>BO-CH-03</t>
   </si>
   <si>
-    <t>스토어 정보 수정의 기본정보 탭 지원언어 아래에 알리페이 노출 설정을, 버튼 및 메신저 설정 탭에 항목마다 알리페이 ON/OFF 열을 추가한다. 스토어는 언어와 무관한 한 건이라 설정 하나가 모든 언어에 적용된다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">■ 기본정보 탭
+    <t>스토어 정보 수정의 기본정보 섹션 지원언어 아래에 알리페이 노출 설정을, 버튼 및 메신저 설정 섹션에 항목마다 알리페이 ON/OFF 열을 추가한다. 스토어는 언어와 무관한 한 건이라 설정 하나가 모든 언어에 적용된다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 기본정보 섹션
 - 알리페이 노출 : 라디오 (노출 / 미노출), 디폴트 노출
 - 위치 : 지원언어 바로 아래. 위 두 줄(카테고리·지원언어)이 노출 축, 아래 네 줄(대표번호·사업자명·사업자번호·이메일)이 사업자 정보
 - 라디오 아래 한 줄 "지원언어와 무관하게 이 설정 하나가 모든 언어에 적용됩니다."
-■ 버튼 및 메신저 설정 탭 (BO-CH-10 공통 구조)
+■ 버튼 및 메신저 설정 섹션 (BO-CH-10 공통 구조)
 - 항목 표 : 행 = 상담접수 / 채팅(신설) / 상담접수·채팅 통합 표시 / 외부링크 설정 / 메신저 설정 / 예약. 열 = 웹 ON·OFF, 알리페이 ON·OFF
   ㄴ 알리페이 열의 외부링크·메신저는 비활성 고정 + 안내
   ㄴ 상담접수·채팅·통합 표시는 서로 독립된 버튼. 통합 표시는 기존 문의하기 버튼 그대로이고 켜면 다른 항목과 같이 1자리
-  ㄴ 예약은 예약설정 탭에서 예약을 켠 뒤에만. 웹·알리페이 열 모두 같다
+  ㄴ 예약은 예약설정 섹션에서 예약을 켠 뒤에만. 웹·알리페이 열 모두 같다
   ㄴ 항목마다 프런트 하단 독립된 자리. 서로 묶어 세는 항목 없음. 자리 수는 열마다 최대 둘
 - 메신저 채널·URL·QR : 기존 언어별 구조 그대로. 알리페이 열과 무관
-- 안내 박스 : 알리페이 열 ON 없음 시 "알리페이 앱 버튼이 없어 알리페이에 노출되지 않습니다.” 기본정보 탭에서는 “알리페이 앱 버튼이 없어 이 스토어와 스토어 상품 N건이 알리페이에 노출되지 않습니다. 버튼 및 메신저 설정에서 1개 이상 켜면 노출됩니다."
+- 안내 박스 : 알리페이 열 ON 없음 시 “알리페이 앱 버튼이 없어 알리페이에 노출되지 않습니다.” 기본정보 섹션에서는 “알리페이 앱 버튼이 없어 이 스토어와 스토어 상품 N건이 알리페이에 노출되지 않습니다. 버튼 및 메신저 설정에서 1개 이상 켜면 노출됩니다.”
 - 알리페이 노출이 노출인데 알리페이 열에 ON이 없는 상태로 저장하면 저장 시 확인 "알리페이 앱 버튼이 없습니다. 저장하면 스토어가 알리페이에 노출되지 않습니다. 저장할까요?" 어떤 행을 꺼서 비었든 같다. 행을 끄는 순간에는 확인을 띄우지 않는다
-■ 기본정보 탭 · 미노출 선택 시
+■ 기본정보 섹션 · 미노출 선택 시
 - 라디오 아래 안내 박스 "미노출로 저장하면 이 스토어 상품 N건도 알리페이에 노출되지 않습니다." 고르는 순간에는 확인을 띄우지 않는다
 - 영향받는 상품·배너·기획전이 있으면 저장 시 확인 모달(BO-CH-03-mdl)
 ■ 스토어 소개
@@ -385,7 +385,7 @@
   </si>
   <si>
     <t xml:space="preserve">- 스토어의 알리페이 노출 설정이 미노출이면 그 스토어의 상품이 모든 언어에서 함께 숨겨진다(조건 ③). 스토어를 되돌리면 그 스토어의 상품은 원래 값대로 돌아온다
-- 스토어의 알리페이 열이 비면 스토어와 그 스토어의 상품이 모두 숨겨진다(조건 ③). 이때 기본정보 탭 알리페이 노출 라디오 아래에 “알리페이 앱 버튼이 없어 이 스토어와 스토어 상품 N건이 알리페이에 노출되지 않습니다. 버튼 및 메신저 설정에서 1개 이상 켜면 노출됩니다.” 안내를 둔다
+- 스토어의 알리페이 열이 비면 스토어와 그 스토어의 상품이 모두 숨겨진다(조건 ③). 이때 기본정보 섹션 알리페이 노출 라디오 아래에 “알리페이 앱 버튼이 없어 이 스토어와 스토어 상품 N건이 알리페이에 노출되지 않습니다. 버튼 및 메신저 설정에서 1개 이상 켜면 노출됩니다.” 안내를 둔다
 - 스토어가 노출이고 알리페이 열에 예약만 켜져 있으면 기본 설정 상품은 알리페이 열이 비어 미노출(사유 알리페이 버튼 미설정)
 - 스토어의 알리페이 버튼 설정 변경은 기본 설정인 상품 전부에 즉시 적용
 - 공개 여부가 비공개여도 알리페이 노출 라디오를 잠그지 않는다. 신규 스토어가 비공개로 시작하므로 공개 전에 미리 정해 둘 수 있어야 한다. 안내 문구도 없음</t>
@@ -397,7 +397,7 @@
     <t>BO-CH-03-e1</t>
   </si>
   <si>
-    <t>미노출이면 버튼 및 메신저 설정 탭의 알리페이 열 전체를 비활성으로 잠근다. 노출로 바꾸면 열린다. 상품(BO-CH-01-e1)과 같은 동작이다.</t>
+    <t>미노출이면 버튼 및 메신저 설정 섹션의 알리페이 열 전체를 비활성으로 잠근다. 노출로 바꾸면 열린다. 상품(BO-CH-01-e1)과 같은 동작이다.</t>
   </si>
   <si>
     <t xml:space="preserve">■ 잠금
@@ -419,7 +419,7 @@
   </si>
   <si>
     <t xml:space="preserve">■ 안내 박스
-- “알리페이 앱 버튼이 없어 알리페이에 노출되지 않습니다.” 기본정보 탭에서는 “알리페이 앱 버튼이 없어 이 스토어와 스토어 상품 N건이 알리페이에 노출되지 않습니다. 버튼 및 메신저 설정에서 1개 이상 켜면 노출됩니다.”</t>
+- “알리페이 앱 버튼이 없어 알리페이에 노출되지 않습니다.” 기본정보 섹션에서는 “알리페이 앱 버튼이 없어 이 스토어와 스토어 상품 N건이 알리페이에 노출되지 않습니다. 버튼 및 메신저 설정에서 1개 이상 켜면 노출됩니다.”</t>
   </si>
   <si>
     <t>- 목록(BO-CH-04) 사유 = 알리페이 버튼 미설정</t>
@@ -428,20 +428,20 @@
     <t>예약설정 미사용일 때 예약 행 잠금</t>
   </si>
   <si>
-    <t>예약설정 탭의 예약 사용이 미사용인 스토어</t>
+    <t>예약설정 섹션의 예약 사용이 미사용인 스토어</t>
   </si>
   <si>
     <t>BO-CH-03-e3</t>
   </si>
   <si>
-    <t>예약설정 탭에서 예약을 켜지 않은 스토어는 버튼 및 메신저 설정의 예약 행을 웹 열·알리페이 열 모두 켤 수 없다.</t>
+    <t>예약설정 섹션에서 예약을 켜지 않은 스토어는 버튼 및 메신저 설정의 예약 행을 웹 열·알리페이 열 모두 켤 수 없다.</t>
   </si>
   <si>
     <t xml:space="preserve">■ 예약 행
 - 웹 ON·OFF, 알리페이 ON·OFF 라디오 전부 비활성. 표시는 OFF, 저장값은 유지
 - 행 오른쪽 안내 "예약설정에서 예약을 사용하면 켤 수 있습니다."
 ■ 해제
-- 예약설정 탭에서 예약 사용으로 바꾸면 즉시 열린다</t>
+- 예약설정 섹션에서 예약 사용으로 바꾸면 즉시 열린다</t>
   </si>
   <si>
     <t>- 예약을 미사용으로 되돌리면 켜 둔 예약 행은 판정에서 빠진다. 그래서 알리페이 열이 비면 저장 시 확인(BO-CH-03)이 뜬다</t>
@@ -450,16 +450,16 @@
     <t>PRD v2.15 7장 버튼 종류 표</t>
   </si>
   <si>
-    <t>기본정보 탭에서 미노출 선택</t>
-  </si>
-  <si>
-    <t>기본정보 탭의 알리페이 노출을 미노출로 선택</t>
+    <t>기본정보 섹션에서 미노출 선택</t>
+  </si>
+  <si>
+    <t>기본정보 섹션의 알리페이 노출을 미노출로 선택</t>
   </si>
   <si>
     <t>BO-CH-03-e4</t>
   </si>
   <si>
-    <t>기본정보 탭에서 미노출을 고르면 라디오 아래 안내 박스에 이 스토어 상품 수를 보여준다. 고르는 순간에는 확인을 띄우지 않고, 저장할 때 영향받는 항목이 있으면 확인 모달(BO-CH-03-mdl)을 띄운다.</t>
+    <t>기본정보 섹션에서 미노출을 고르면 라디오 아래 안내 박스에 이 스토어 상품 수를 보여준다. 고르는 순간에는 확인을 띄우지 않고, 저장할 때 영향받는 항목이 있으면 확인 모달(BO-CH-03-mdl)을 띄운다.</t>
   </si>
   <si>
     <t xml:space="preserve">■ 안내 박스 (라디오 아래)
@@ -476,7 +476,7 @@
     <t>알리페이 미노출 저장 확인 모달</t>
   </si>
   <si>
-    <t>기본정보 탭에서 미노출 선택 후 저장</t>
+    <t>기본정보 섹션에서 미노출 선택 후 저장</t>
   </si>
   <si>
     <t>BO-CH-03-mdl</t>
@@ -743,7 +743,7 @@
 - 인플루언서 기획전에는 밖으로 나가는 링크가 없다. 담은 상품의 알리페이 버튼 조건은 상품 판정에 이미 들어 있다
 - 패스워드는 성과 페이지 접근용이라 공개 페이지와 판정에 관계없다. 담은 상품의 언어는 보지 않는다
 ■ 직접입력
-- 입력한 주소를 /products/{id}, /stores/{id}, /collections/{id}, /influencers/{id} 패턴으로 파싱한다. 앞의 언어 경로(/en, /zh-CN 등)와 ?·# 뒤는 무시한다
+- 입력한 주소를 /products/{id}, /stores/{id}, /collections/{id}, /influencers/{id} 패턴으로 파싱한다. 앞의 언어 경로(/en, /zh 등)와 ?·# 뒤는 무시한다
 - 패턴에 맞으면 그 대상(상품·스토어·기획전·인플루언서 기획전)의 판정을 그대로 읽는다. 대상이 없으면 사유 노출 대상 없음
 - 패턴에 맞지 않으면(카테고리·검색·홈 등 목록 페이지) 대상을 특정할 수 없어 판정을 건너뛴다. 알리페이 노출이 노출이면 노출. 안내 없음
 - 다른 사이트의 절대 주소(다른 도메인, javascript: 등)는 외부 사이트 연결로 보고 알리페이에 노출하지 않는다. 판정 옆에 "직접입력 · 외부 사이트". 우리 도메인의 절대 주소는 경로만 읽어 위와 같이 판정한다</t>
@@ -918,7 +918,7 @@
 - 담는 종류가 달라지는 유형으로 바꾸면 앞 유형에 담아 둔 항목은 비운다. 추천상품·특가·TOP10 사이의 전환은 담은 상품을 유지한다. 확인 문구 "유형을 변경하면 담은 상품 N건이 삭제되고 스토어만 담을 수 있습니다. 스토어를 1개 이상 담아야 저장할 수 있습니다. 변경할까요?" 병원에서 상품 유형으로 바꿀 때는 상품과 스토어를 바꿔 쓴다. 비운 상태로는 저장할 수 없어 그 자리에서 새 유형의 항목을 담아야 한다
 - 안의 항목이 다시 생기면 별도 조작 없이 노출
 - 담은 것이 있는데 전부 보이지 않는 경우는 차단하지 않는다. 원인이 그 상품·스토어 쪽 설정이라 이 화면에서 고칠 수 없고, 대상이 돌아오면 기획전도 자동 복구된다. 이 화면의 차단은 구성 항목 0건
-- 저장 검사 순서 = ① 버튼 개수 상한 → ② 구성 항목 0건 → ③ 확인(기획전은 노출 가능 항목 0건). ①②에 걸리면 확인을 띄우지 않고 막는다
+- 저장 검사 순서 = ① 구성 항목 0건 → ② 확인(노출 가능 항목 0건). ①에 걸리면 확인을 띄우지 않고 막는다. 기획전에는 하단 버튼이 없어 개수 상한 검사가 없다
 - 대상 언어(중국어(간체)·중국어(번체)·영어)가 아닌 기획전은 알리페이 노출 라디오가 노출로 고정 잠김. 안내 문구는 두지 않는다
 - 구성 항목 표의 체크박스로 여러 건을 고를 수 있다. 하나도 고르지 않으면 선택 삭제 버튼은 비활성</t>
   </si>
@@ -1039,7 +1039,7 @@
     <t>버튼 설정 영역 (웹·알리페이 두 열, 채팅 항목 신설)</t>
   </si>
   <si>
-    <t>BO 상품 관리자설정 탭 / 스토어 버튼 및 메신저 설정 탭</t>
+    <t>BO 상품 관리자설정 탭 / 스토어 버튼 및 메신저 설정 섹션</t>
   </si>
   <si>
     <t>BO-CH-10</t>
@@ -1055,7 +1055,7 @@
 - 광고 수정은 모달이다. 라이브 520px(2026-09-07 캡처 확인)에서 700px로 넓힌다
 - 좁은 화면 : 항목·웹·알리페이는 폭 유지, 안내 열이 먼저 줄고 자리가 없으면 그 행 아래로 내린다. 가로 잘림 없음
 - 행 : 상담접수 / 채팅(신설) / 상담접수·채팅 통합 표시 / 외부링크 설정 / 메신저 설정 / 예약(스토어만)
-- 셀 : ON·OFF 라디오. 필수(*) 표시는 기존 그대로
+- 셀 : ON·OFF 라디오. 행 라벨에 필수(*) 표시를 두지 않는다. 활성화·히든 여부 라디오와 같다
 ■ 항목별 알리페이 열 규칙
 - 상담접수 : 가능 (자체 기능). 채팅과 완전히 독립
 - 채팅 : 가능. 인앱 채팅, 웹 열에서도 켤 수 있다. 상담접수와 완전히 독립
@@ -1064,9 +1064,9 @@
 - 통합 표시 행 오른쪽에는 상시 “기존 문의하기 버튼입니다. 다른 항목과 같이 독립된 버튼이라 켜면 1개로 셉니다.”
 - 외부링크 설정 : 비활성 고정 + 안내 “알리페이 앱 미지원 항목입니다.”
 - 메신저 설정 : 비활성 고정 + 같은 안내. 채널·URL·QR 입력은 기존 언어별 구조 그대로. 언어별 입력 영역 안내는 “메신저 설정을 켜면 언어별로 1개씩 등록할 수 있습니다.”
-- 예약 : 가능. 예약설정 탭에서 예약을 켠 뒤에만. 조건 미충족 시 행 오른쪽 안내 “예약설정에서 예약을 사용하면 켤 수 있습니다.”
-- 예약설정 탭의 예약 사용 항목 아래 한 줄 “예약을 사용해야 버튼 및 메신저 설정에서 예약 버튼을 켤 수 있습니다.”
-- 예약을 미사용으로 바꾸면 예약설정 탭의 예약 사용 항목 아래 “예약 미사용 상태입니다. 예약 버튼은 웹·알리페이 앱 모두 꺼집니다. 설정값은 유지됩니다.”
+- 예약 : 가능. 예약설정 섹션에서 예약을 켠 뒤에만. 조건 미충족 시 행 오른쪽 안내 “예약설정에서 예약을 사용하면 켤 수 있습니다.”
+- 예약설정 섹션의 예약 사용 항목 아래 한 줄 “예약을 사용해야 버튼 및 메신저 설정에서 예약 버튼을 켤 수 있습니다.”
+- 예약을 미사용으로 바꾸면 예약설정 섹션의 예약 사용 항목 아래 “예약 미사용 상태입니다. 예약 버튼은 웹·알리페이 앱 모두 꺼집니다. 설정값은 유지됩니다.”
 ■ 상한
 - 버튼 자리 계산 : 상담접수·채팅·통합 표시(문의하기)·외부링크·메신저·예약 모두 각각 1자리. 서로 묶어 세는 항목 없음. 켜져 있는 유효 항목 수가 곧 자리 수
 - 웹 열 자리 최대 둘, 알리페이 열 자리 최대 둘. 동시에 가능
@@ -1266,7 +1266,7 @@
     <t xml:space="preserve">■ 내부 연결
 - 정식 경로는 상품 추가·스토어 추가 버튼이다. 이미 있는 기능이고 이번 범위에서 손대지 않는다
 ■ 에디터 링크 도구
-- 다른 사이트 주소·동영상·SNS 삽입 차단 + 안내 문구 (쉬운 말). 붙여넣기 유입분은 저장 시 제거
+- 다른 사이트 주소·동영상·SNS 삽입 차단 + 안내 문구 (쉬운 말). 붙여넣기 유입분은 저장 시 제거 + 저장 후 안내 "다른 사이트 주소 N개, 동영상·SNS M개를 지웠어요." 둘 중 하나만 있으면 그 항목만 쓴다
 - 링크 도구로 직접 입력한 내부 주소(우리 도메인의 절대 URL 포함)는 상대 경로로 저장한다. 어드민 매거진(BO-CH-07)과 같은 처리</t>
   </si>
   <si>
@@ -3566,7 +3566,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="32" ht="355" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" ht="368.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>13</v>
       </c>

--- a/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
+++ b/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
@@ -1969,6 +1969,7 @@
 - (c) 구성 항목 0건 기획전 집계 → 값 유지, 목록으로 넘겨 사장님이 배포 전에 항목을 담거나 비활성으로 정리를 마친다
 - (d) 연결 대상이 비활성·기간 종료·언어 불일치인 배너 집계 → 배포와 동시에 알리페이 미노출로 바뀜. 배너 자체가 기간 종료면 제외. 이미 웹에서도 안 보이는 대상이라 정리를 기다리지 않고 배포한다
 - (e) 같은 유형 값·언어로 둘 이상인 기획전 유형 레코드 집계 → 사장님이 배포 전에 하나로 합치고 붙은 기획전·가리키는 배너를 남는 레코드로 이동해 정리를 마친다. 값 유지
+- (f) 알리페이 열 채우기 규칙 적용 후 알리페이 열이 비게 되는 스토어·상품 집계 → 스토어 목록, 각 스토어의 대상 언어 상품 수, 대상 언어 상품 전체 대비 비율. 언어별(간체·번체·영어) 알리페이 통과 예정 건수도 함께 뽑는다. 정리 대상이 아니라 판단 자료다. 비율이 크면 마이그레이션 규칙을 다시 정한다(알리페이 열이 비는 스토어에 상담접수 자동 ON 검토)
 ■ 알리페이 열 채우기 규칙
 - 웹 ON인 상담접수, 상담접수·채팅 통합 표시, 예약 → 알리페이 ON
 - 웹 메신저 ON → 알리페이 채팅 ON
@@ -4721,7 +4722,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="65" ht="220" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" ht="247" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>430</v>
       </c>

--- a/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
+++ b/_wiki_tmp/알리페이채널분기_기능정의서_v2.16_20260918.xlsx
@@ -1392,8 +1392,8 @@
 - 저장하면 목록과 고객 화면에 즉시 반영된다. 참조 대상이 바뀌어 결과가 달라지는 경우도 같다
 - 이 기준을 지킬 수 있게 만든다. 구현 방식과 수치는 개발이 정한다
 - 결과가 다시 계산되는 경우 전체 목록은 PRD 9장. 기획전 유형 레코드 변경(옛·새 유형 배너 모두), 유형 레코드 생성·삭제·언어 변경, 대상의 활성·기간·공개·삭제 변경, 기간 경계 날짜 경과를 포함
-■ 리뷰 (신규)
-- 알리페이 회원이 쓴 리뷰는 알리페이 채널에서만, 웹 회원이 쓴 리뷰는 웹에서만 노출한다. 리뷰 수·평점 등 집계도 채널별로 따로 계산한다
+■ 리뷰 (작성자 표시명)
+- 리뷰는 채널을 나누지 않는다. 웹 회원과 알리페이 회원의 리뷰가 두 채널 모두에서 보이고, 리뷰 수·평점 집계도 하나다. 새 채널을 리뷰 0건으로 열지 않기 위해서다
 - 작성자 표시명은 알리페이가 주는 표시용 값(닉네임 등)이 있으면 그 값을 쓴다. 알리페이 식별자는 고객 화면에 노출하지 않는다
 - 표시용 값을 못 받으면(프로필 제공 거부 포함) “알리페이 회원”으로 표시한다. 난수형 식별자는 쓰지 않는다. 채팅에서 보이는 이름도 같은 규칙
 - 개발 확인 항목 : 알리페이 개발문서(가맹점 OAuth·회원정보 API) 기준으로 ① 닉네임·아바타 제공 가능 여부 ② 기본 식별 권한만으로 오는지, 프로필 제공 동의(auth_user 계열)가 필요한지 ③ 중국·홍콩 월렛이 같은지 확인해 결과를 반영한다</t>
